--- a/ACQ_TGT_merger_model.xlsx
+++ b/ACQ_TGT_merger_model.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="xl"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -15,11 +15,6 @@
     <sheet name="Ownership &amp; Credit" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
